--- a/temp_users_file.xlsx
+++ b/temp_users_file.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="757">
   <si>
     <t>Name</t>
   </si>
@@ -62,7 +62,10 @@
     <t>System Administrator</t>
   </si>
   <si>
-    <t>14/01/2022</t>
+    <t>18/02/2022</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
   </si>
   <si>
     <t>On-site</t>
@@ -95,1272 +98,1284 @@
     <t>EMP7603</t>
   </si>
   <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>18/02/2025</t>
+  </si>
+  <si>
+    <t>Team Lead User</t>
+  </si>
+  <si>
+    <t>employee</t>
+  </si>
+  <si>
+    <t>Akshay Surendran</t>
+  </si>
+  <si>
+    <t>akshay@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6538</t>
+  </si>
+  <si>
+    <t>17/01/2026</t>
+  </si>
+  <si>
+    <t>Alshana Abdulla</t>
+  </si>
+  <si>
+    <t>alshana@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP8900</t>
+  </si>
+  <si>
+    <t>Ambily MS</t>
+  </si>
+  <si>
+    <t>ambily@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1879</t>
+  </si>
+  <si>
+    <t>ambily@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP9585</t>
+  </si>
+  <si>
+    <t>Amrutha  KS</t>
+  </si>
+  <si>
+    <t>amrutha@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP7246</t>
+  </si>
+  <si>
+    <t>18/05/2025</t>
+  </si>
+  <si>
+    <t>Anagha Nisakar</t>
+  </si>
+  <si>
+    <t>anagha@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2144</t>
+  </si>
+  <si>
+    <t>Anandhu T Prasannan</t>
+  </si>
+  <si>
+    <t>anandhu@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3776</t>
+  </si>
+  <si>
+    <t>Aneetta  Laila</t>
+  </si>
+  <si>
+    <t>aneetta@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP5503</t>
+  </si>
+  <si>
+    <t>Anish Mohan K</t>
+  </si>
+  <si>
+    <t>anish@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1126</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>Fasna KK</t>
+  </si>
+  <si>
+    <t>project-manager</t>
+  </si>
+  <si>
+    <t>Anna Motshagen</t>
+  </si>
+  <si>
+    <t>anna@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP9876</t>
+  </si>
+  <si>
+    <t>Anto  Job Thankachan</t>
+  </si>
+  <si>
+    <t>anto@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP9366</t>
+  </si>
+  <si>
+    <t>apexfunding</t>
+  </si>
+  <si>
+    <t>apexfunding@gmail.com</t>
+  </si>
+  <si>
+    <t>EMP1615</t>
+  </si>
+  <si>
+    <t>Ardra  Suresh</t>
+  </si>
+  <si>
+    <t>ardra@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4161</t>
+  </si>
+  <si>
+    <t>Arjun A  Praji</t>
+  </si>
+  <si>
+    <t>arjun@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP7645</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>Banid Azin TT</t>
+  </si>
+  <si>
+    <t>banid@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP9107</t>
+  </si>
+  <si>
+    <t>Basil  Mirshab</t>
+  </si>
+  <si>
+    <t>basilmirshab@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4699</t>
+  </si>
+  <si>
+    <t>wfwefweww</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
+  </si>
+  <si>
+    <t>WFH</t>
+  </si>
+  <si>
+    <t>biby@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP4521</t>
+  </si>
+  <si>
+    <t>Binsitha KP</t>
+  </si>
+  <si>
+    <t>binsitha@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP9583</t>
+  </si>
+  <si>
+    <t>Career</t>
+  </si>
+  <si>
+    <t>career@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1527</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>cyril</t>
+  </si>
+  <si>
+    <t>cyril@zinops.com</t>
+  </si>
+  <si>
+    <t>EMP7849</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>design@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6016</t>
+  </si>
+  <si>
+    <t>Devnasree  P</t>
+  </si>
+  <si>
+    <t>devnasree@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6102</t>
+  </si>
+  <si>
+    <t>Fabian Sempf</t>
+  </si>
+  <si>
+    <t>fabians@mercantilepacific.com</t>
+  </si>
+  <si>
+    <t>EMP4574</t>
+  </si>
+  <si>
+    <t>fabians@mercantilepacific.om</t>
+  </si>
+  <si>
+    <t>EMP4384</t>
+  </si>
+  <si>
+    <t>Fahad  KC</t>
+  </si>
+  <si>
+    <t>fahad@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3229</t>
+  </si>
+  <si>
+    <t>Fahana N P</t>
+  </si>
+  <si>
+    <t>fahana@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP8838</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>Farhan  Handover</t>
+  </si>
+  <si>
+    <t>farhan@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4434</t>
+  </si>
+  <si>
+    <t>Faris</t>
+  </si>
+  <si>
+    <t>faris@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1977</t>
+  </si>
+  <si>
+    <t>09/01/2016</t>
+  </si>
+  <si>
+    <t>Farzin Mohammed  V</t>
+  </si>
+  <si>
+    <t>farzin@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1435</t>
+  </si>
+  <si>
+    <t>Faseela KK</t>
+  </si>
+  <si>
+    <t>faseela@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1463</t>
+  </si>
+  <si>
+    <t>faseela@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP9804</t>
+  </si>
+  <si>
+    <t>Fida  Ashraf O</t>
+  </si>
+  <si>
+    <t>fida@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4221</t>
+  </si>
+  <si>
+    <t>fida@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP2302</t>
+  </si>
+  <si>
+    <t>Abdul Hafeelu</t>
+  </si>
+  <si>
+    <t>hafeelu@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4230</t>
+  </si>
+  <si>
+    <t>Senior Quality Analyst</t>
+  </si>
+  <si>
+    <t>06/03/2025</t>
+  </si>
+  <si>
+    <t>05/03/2002</t>
+  </si>
+  <si>
+    <t>Hafis C P</t>
+  </si>
+  <si>
+    <t>hafis@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3326</t>
+  </si>
+  <si>
+    <t>IOCOD</t>
+  </si>
+  <si>
+    <t>info@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3441</t>
+  </si>
+  <si>
+    <t>Muhammed Jabir C</t>
+  </si>
+  <si>
+    <t>jabir@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3675</t>
+  </si>
+  <si>
+    <t>Muhammed Jasim K</t>
+  </si>
+  <si>
+    <t>jasim@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/ 1040</t>
+  </si>
+  <si>
+    <t>Team Lead</t>
+  </si>
+  <si>
+    <t>Jerish  Edward</t>
+  </si>
+  <si>
+    <t>jerish@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1330</t>
+  </si>
+  <si>
+    <t>Jestina  Thomson</t>
+  </si>
+  <si>
+    <t>jestina@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2286</t>
+  </si>
+  <si>
+    <t>Jinesh KP</t>
+  </si>
+  <si>
+    <t>jinesh@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2015</t>
+  </si>
+  <si>
+    <t>Jishad P</t>
+  </si>
+  <si>
+    <t>jishad@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP7301</t>
+  </si>
+  <si>
+    <t>Jithin A</t>
+  </si>
+  <si>
+    <t>jithin@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4232</t>
+  </si>
+  <si>
+    <t>Keerthana  Murali</t>
+  </si>
+  <si>
+    <t>keerthanamurali@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3409</t>
+  </si>
+  <si>
+    <t>kk.fasil</t>
+  </si>
+  <si>
+    <t>kk.fasil@yahoo.com</t>
+  </si>
+  <si>
+    <t>EMP6579</t>
+  </si>
+  <si>
+    <t>laya@easify.app</t>
+  </si>
+  <si>
+    <t>EMP8549</t>
+  </si>
+  <si>
+    <t>lisak</t>
+  </si>
+  <si>
+    <t>lisak@sbacfunding.com</t>
+  </si>
+  <si>
+    <t>EMP3598</t>
+  </si>
+  <si>
+    <t>mailme</t>
+  </si>
+  <si>
+    <t>mailme@rohitwanchoo.com</t>
+  </si>
+  <si>
+    <t>EMP7089</t>
+  </si>
+  <si>
+    <t>melvin@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP2473</t>
+  </si>
+  <si>
+    <t>Merin  Mohan</t>
+  </si>
+  <si>
+    <t>merin@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP5275</t>
+  </si>
+  <si>
+    <t>Mubashir</t>
+  </si>
+  <si>
+    <t>mubashir@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP7549</t>
+  </si>
+  <si>
+    <t>muhammedshameem880@gmail.com</t>
+  </si>
+  <si>
+    <t>EMP9867</t>
+  </si>
+  <si>
+    <t>Nauf  KG</t>
+  </si>
+  <si>
+    <t>nauf@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP5393</t>
+  </si>
+  <si>
+    <t>Neda Ashraf</t>
+  </si>
+  <si>
+    <t>neda@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2711</t>
+  </si>
+  <si>
+    <t>Neethu k</t>
+  </si>
+  <si>
+    <t>neethu.k@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2509</t>
+  </si>
+  <si>
+    <t>Neethu  Martin</t>
+  </si>
+  <si>
+    <t>neethu@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP8723</t>
+  </si>
+  <si>
+    <t>neethu@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP9485</t>
+  </si>
+  <si>
+    <t>Nejla K P</t>
+  </si>
+  <si>
+    <t>nejla@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1043</t>
+  </si>
+  <si>
+    <t>HR Associate</t>
+  </si>
+  <si>
+    <t>03/11/2021</t>
+  </si>
+  <si>
+    <t>new hr</t>
+  </si>
+  <si>
+    <t>hr</t>
+  </si>
+  <si>
+    <t>Nihal  PP</t>
+  </si>
+  <si>
+    <t>nihal@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3197</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>office@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3917</t>
+  </si>
+  <si>
+    <t>Patrick Mevis</t>
+  </si>
+  <si>
+    <t>patrick@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP7264</t>
+  </si>
+  <si>
+    <t>Pranav</t>
+  </si>
+  <si>
+    <t>pranav@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2488</t>
+  </si>
+  <si>
+    <t>Priya TP</t>
+  </si>
+  <si>
+    <t>priya@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1349</t>
+  </si>
+  <si>
+    <t>IOCOD TESTING MMP</t>
+  </si>
+  <si>
+    <t>qaiocod@gmail.com</t>
+  </si>
+  <si>
+    <t>EMP5893</t>
+  </si>
+  <si>
+    <t>Raneesa  K</t>
+  </si>
+  <si>
+    <t>raneesa@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3561</t>
+  </si>
+  <si>
+    <t>Muhammed Rashid P</t>
+  </si>
+  <si>
+    <t>rashidp@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP7869</t>
+  </si>
+  <si>
+    <t>rina@easify.app</t>
+  </si>
+  <si>
+    <t>EMP7642</t>
+  </si>
+  <si>
+    <t>Rishab Haridas</t>
+  </si>
+  <si>
+    <t>rishab@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3535</t>
+  </si>
+  <si>
+    <t>Rishana SKP</t>
+  </si>
+  <si>
+    <t>rishana@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6997</t>
+  </si>
+  <si>
+    <t>rishana@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP3046</t>
+  </si>
+  <si>
+    <t>Rohith  K</t>
+  </si>
+  <si>
+    <t>rohith@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1004</t>
+  </si>
+  <si>
+    <t>Sabil K</t>
+  </si>
+  <si>
+    <t>sabil@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4631</t>
+  </si>
+  <si>
+    <t>sagar s kumar</t>
+  </si>
+  <si>
+    <t>sagar@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4896</t>
+  </si>
+  <si>
+    <t>Sahal Muhammed KK</t>
+  </si>
+  <si>
+    <t>sahal@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2846</t>
+  </si>
+  <si>
+    <t>Laravel Developer</t>
+  </si>
+  <si>
+    <t>15/11/2025</t>
+  </si>
+  <si>
+    <t>sales</t>
+  </si>
+  <si>
+    <t>sales@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6636</t>
+  </si>
+  <si>
+    <t>saranya iocod</t>
+  </si>
+  <si>
+    <t>saranya@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4093</t>
+  </si>
+  <si>
+    <t>saranya@zinops.com</t>
+  </si>
+  <si>
+    <t>EMP2137</t>
+  </si>
+  <si>
+    <t>Shahana Sherin</t>
+  </si>
+  <si>
+    <t>shahana@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP5832</t>
+  </si>
+  <si>
+    <t>Muhammed Shaheer P</t>
+  </si>
+  <si>
+    <t>shaheer@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2012</t>
+  </si>
+  <si>
+    <t>shameem@mca.plus</t>
+  </si>
+  <si>
+    <t>EMP8421</t>
+  </si>
+  <si>
+    <t>P Mohamed Shanid</t>
+  </si>
+  <si>
+    <t>shanid@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP9578</t>
+  </si>
+  <si>
+    <t>Sherin  Thomas</t>
+  </si>
+  <si>
+    <t>sherin@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3530</t>
+  </si>
+  <si>
+    <t>Shifana KS</t>
+  </si>
+  <si>
+    <t>shifana@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP1294</t>
+  </si>
+  <si>
+    <t>Sreehari PO</t>
+  </si>
+  <si>
+    <t>sreeharipo@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6974</t>
+  </si>
+  <si>
+    <t>Sreejesh CV</t>
+  </si>
+  <si>
+    <t>sreejeshk@mercantilepacific.com</t>
+  </si>
+  <si>
+    <t>EMP4370</t>
+  </si>
+  <si>
+    <t>Suvidya Raj TM</t>
+  </si>
+  <si>
+    <t>suvidya@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4133</t>
+  </si>
+  <si>
+    <t>Fathima Thamanna  Filsher</t>
+  </si>
+  <si>
+    <t>thamanna@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP6025</t>
+  </si>
+  <si>
+    <t>Uvais Mohammad</t>
+  </si>
+  <si>
+    <t>uvais@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP9981</t>
+  </si>
+  <si>
+    <t>Vijay Mathew</t>
+  </si>
+  <si>
+    <t>vijay@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP4240</t>
+  </si>
+  <si>
+    <t>YASHIN  TM</t>
+  </si>
+  <si>
+    <t>yashin@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP3165</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>Zainab  SH</t>
+  </si>
+  <si>
+    <t>zainab@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP2021</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>hr@example.com</t>
+  </si>
+  <si>
+    <t>hr/11</t>
+  </si>
+  <si>
+    <t>15/12/2025</t>
+  </si>
+  <si>
+    <t>PM User</t>
+  </si>
+  <si>
+    <t>pm@example.com</t>
+  </si>
+  <si>
+    <t>pm/11</t>
+  </si>
+  <si>
+    <t>17/12/2025</t>
+  </si>
+  <si>
+    <t>lead@example.com</t>
+  </si>
+  <si>
+    <t>tl/11</t>
+  </si>
+  <si>
+    <t>team-lead</t>
+  </si>
+  <si>
+    <t>Employee User</t>
+  </si>
+  <si>
+    <t>employee@example.com</t>
+  </si>
+  <si>
+    <t>emp/11</t>
+  </si>
+  <si>
+    <t>17/01/2023</t>
+  </si>
+  <si>
+    <t>udemy IOCOD</t>
+  </si>
+  <si>
+    <t>udemy@iocod.com</t>
+  </si>
+  <si>
+    <t>ud1212</t>
+  </si>
+  <si>
+    <t>Olivia Davis</t>
+  </si>
+  <si>
+    <t>olivia@gmail.com</t>
+  </si>
+  <si>
+    <t>emp/132</t>
+  </si>
+  <si>
+    <t>02/01/2022</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>name@gmail.com</t>
+  </si>
+  <si>
+    <t>name1212</t>
+  </si>
+  <si>
+    <t>24/12/2025</t>
+  </si>
+  <si>
+    <t>Abhiram  Santhosh</t>
+  </si>
+  <si>
+    <t>abhiramsanthosh@iocod.com</t>
+  </si>
+  <si>
+    <t>abhiram/11</t>
+  </si>
+  <si>
+    <t>21/02/2025</t>
+  </si>
+  <si>
+    <t>20/02/2025</t>
+  </si>
+  <si>
+    <t>Vaishnav VC</t>
+  </si>
+  <si>
+    <t>Vaishnav@iocod.com</t>
+  </si>
+  <si>
+    <t>emp12</t>
+  </si>
+  <si>
+    <t>Quality Analyst</t>
+  </si>
+  <si>
+    <t>11/12/2025</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>developer@iocod.com</t>
+  </si>
+  <si>
+    <t>emp12121</t>
+  </si>
+  <si>
+    <t>26/12/2025</t>
+  </si>
+  <si>
+    <t>Abhiram Krishna M</t>
+  </si>
+  <si>
+    <t>abhiram@iocod.com</t>
+  </si>
+  <si>
+    <t>Orgnice designation</t>
+  </si>
+  <si>
+    <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>Abhishek M Menon</t>
+  </si>
+  <si>
+    <t>abhishek@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1074</t>
+  </si>
+  <si>
+    <t>Software Developer</t>
+  </si>
+  <si>
+    <t>20/02/2023</t>
+  </si>
+  <si>
+    <t>18/02/2002</t>
+  </si>
+  <si>
+    <t>Adyuth P</t>
+  </si>
+  <si>
+    <t>adyuth@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1063</t>
+  </si>
+  <si>
+    <t>UI/UX Team Lead</t>
+  </si>
+  <si>
+    <t>19/02/2025</t>
+  </si>
+  <si>
+    <t>Muhammed Ahnas K K</t>
+  </si>
+  <si>
+    <t>ahnas@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1016</t>
+  </si>
+  <si>
+    <t>Akash N O</t>
+  </si>
+  <si>
+    <t>akash@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1066</t>
+  </si>
+  <si>
+    <t>17/03/2023</t>
+  </si>
+  <si>
+    <t>Rashid Pathiyil</t>
+  </si>
+  <si>
+    <t>Aleena Joseph</t>
+  </si>
+  <si>
+    <t>aleena@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1122</t>
+  </si>
+  <si>
+    <t>Junior QA Engineer</t>
+  </si>
+  <si>
+    <t>18/07/2024</t>
+  </si>
+  <si>
+    <t>Amaya VS</t>
+  </si>
+  <si>
+    <t>amaya@iocod.com</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>Anagha Ajith</t>
+  </si>
+  <si>
+    <t>anaghaajith@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1143</t>
+  </si>
+  <si>
+    <t>Data Processing Executive</t>
+  </si>
+  <si>
+    <t>17/02/2025</t>
+  </si>
+  <si>
+    <t>Abhijith M</t>
+  </si>
+  <si>
+    <t>Anagha O</t>
+  </si>
+  <si>
+    <t>anaghao@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1076</t>
+  </si>
+  <si>
+    <t>11/08/2023</t>
+  </si>
+  <si>
+    <t>Anandhu Mohanan</t>
+  </si>
+  <si>
+    <t>anandhum@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1142</t>
+  </si>
+  <si>
+    <t>Content Writer</t>
+  </si>
+  <si>
+    <t>Shanosh Kumar TA</t>
+  </si>
+  <si>
+    <t>Anargha G K</t>
+  </si>
+  <si>
+    <t>anargha@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1128</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>Aneesh Paulson M</t>
+  </si>
+  <si>
+    <t>aneesh@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1135</t>
+  </si>
+  <si>
+    <t>Senior Software Developer</t>
+  </si>
+  <si>
+    <t>20/01/2025</t>
+  </si>
+  <si>
+    <t>Fahid Hassan K</t>
+  </si>
+  <si>
+    <t>Anshad P V</t>
+  </si>
+  <si>
+    <t>anshad@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1137</t>
+  </si>
+  <si>
+    <t>03/02/2025</t>
+  </si>
+  <si>
+    <t>Anukrishnan KS</t>
+  </si>
+  <si>
+    <t>anukrishnan@iocod.com</t>
+  </si>
+  <si>
+    <t>Senior Laravel Developer</t>
+  </si>
+  <si>
+    <t>Anurag C K</t>
+  </si>
+  <si>
+    <t>anurag@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1065</t>
+  </si>
+  <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>Anwar Sabith M</t>
+  </si>
+  <si>
+    <t>anwar@iocod.com</t>
+  </si>
+  <si>
+    <t>swfha</t>
+  </si>
+  <si>
+    <t>Arshad Mannilkadavan</t>
+  </si>
+  <si>
+    <t>arshad@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1099</t>
+  </si>
+  <si>
+    <t>UI/UX Designer</t>
+  </si>
+  <si>
+    <t>08/01/2024</t>
+  </si>
+  <si>
+    <t>Mohammad Ashfaqudheen</t>
+  </si>
+  <si>
+    <t>ashfaq@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1079</t>
+  </si>
+  <si>
+    <t>24/08/2023</t>
+  </si>
+  <si>
+    <t>Aswathi Mukundan</t>
+  </si>
+  <si>
+    <t>aswathim@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1098</t>
+  </si>
+  <si>
+    <t>20/12/2023</t>
+  </si>
+  <si>
+    <t>Aswin Vilas P</t>
+  </si>
+  <si>
+    <t>aswin@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1124</t>
+  </si>
+  <si>
+    <t>attendance</t>
+  </si>
+  <si>
+    <t>Attendance@iocod.com</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Badhsha  K</t>
+  </si>
+  <si>
+    <t>badhsha@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1127</t>
+  </si>
+  <si>
+    <t>Muhammed Basil E</t>
+  </si>
+  <si>
+    <t>basil@iocod.com</t>
+  </si>
+  <si>
+    <t>EMP/IIPL/1051</t>
+  </si>
+  <si>
     <t>Flutter Developer</t>
   </si>
   <si>
-    <t>01/01/2026</t>
-  </si>
-  <si>
-    <t>Team Lead User</t>
-  </si>
-  <si>
-    <t>employee</t>
-  </si>
-  <si>
-    <t>Akshay Surendran</t>
-  </si>
-  <si>
-    <t>akshay@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6538</t>
-  </si>
-  <si>
-    <t>Alshana Abdulla</t>
-  </si>
-  <si>
-    <t>alshana@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP8900</t>
-  </si>
-  <si>
-    <t>Ambily MS</t>
-  </si>
-  <si>
-    <t>ambily@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1879</t>
-  </si>
-  <si>
-    <t>ambily@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP9585</t>
-  </si>
-  <si>
-    <t>Amrutha  KS</t>
-  </si>
-  <si>
-    <t>amrutha@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP7246</t>
-  </si>
-  <si>
-    <t>Software Engineer</t>
-  </si>
-  <si>
-    <t>18/05/2025</t>
-  </si>
-  <si>
-    <t>Anagha Nisakar</t>
-  </si>
-  <si>
-    <t>anagha@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2144</t>
-  </si>
-  <si>
-    <t>Anandhu T Prasannan</t>
-  </si>
-  <si>
-    <t>anandhu@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3776</t>
-  </si>
-  <si>
-    <t>Aneetta  Laila</t>
-  </si>
-  <si>
-    <t>aneetta@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP5503</t>
-  </si>
-  <si>
-    <t>Anish Mohan K</t>
-  </si>
-  <si>
-    <t>anish@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1126</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>15/01/2026</t>
-  </si>
-  <si>
-    <t>Fasna KK</t>
-  </si>
-  <si>
-    <t>project-manager</t>
-  </si>
-  <si>
-    <t>Anna Motshagen</t>
-  </si>
-  <si>
-    <t>anna@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP9876</t>
-  </si>
-  <si>
-    <t>Anto  Job Thankachan</t>
-  </si>
-  <si>
-    <t>anto@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP9366</t>
-  </si>
-  <si>
-    <t>apexfunding</t>
-  </si>
-  <si>
-    <t>apexfunding@gmail.com</t>
-  </si>
-  <si>
-    <t>EMP1615</t>
-  </si>
-  <si>
-    <t>Ardra  Suresh</t>
-  </si>
-  <si>
-    <t>ardra@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4161</t>
-  </si>
-  <si>
-    <t>Arjun A  Praji</t>
-  </si>
-  <si>
-    <t>arjun@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP7645</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>Banid Azin TT</t>
-  </si>
-  <si>
-    <t>banid@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP9107</t>
-  </si>
-  <si>
-    <t>Basil  Mirshab</t>
-  </si>
-  <si>
-    <t>basilmirshab@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4699</t>
-  </si>
-  <si>
-    <t>wfwefweww</t>
-  </si>
-  <si>
-    <t>31/12/2025</t>
-  </si>
-  <si>
-    <t>WFH</t>
-  </si>
-  <si>
-    <t>biby@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP4521</t>
-  </si>
-  <si>
-    <t>Binsitha KP</t>
-  </si>
-  <si>
-    <t>binsitha@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP9583</t>
-  </si>
-  <si>
-    <t>Career</t>
-  </si>
-  <si>
-    <t>career@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1527</t>
-  </si>
-  <si>
-    <t>cyril</t>
-  </si>
-  <si>
-    <t>cyril@zinops.com</t>
-  </si>
-  <si>
-    <t>EMP7849</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>design@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6016</t>
-  </si>
-  <si>
-    <t>Devnasree  P</t>
-  </si>
-  <si>
-    <t>devnasree@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6102</t>
-  </si>
-  <si>
-    <t>Fabian Sempf</t>
-  </si>
-  <si>
-    <t>fabians@mercantilepacific.com</t>
-  </si>
-  <si>
-    <t>EMP4574</t>
-  </si>
-  <si>
-    <t>fabians@mercantilepacific.om</t>
-  </si>
-  <si>
-    <t>EMP4384</t>
-  </si>
-  <si>
-    <t>Fahad  KC</t>
-  </si>
-  <si>
-    <t>fahad@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3229</t>
-  </si>
-  <si>
-    <t>Fahana N P</t>
-  </si>
-  <si>
-    <t>fahana@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP8838</t>
-  </si>
-  <si>
-    <t>05/02/2026</t>
-  </si>
-  <si>
-    <t>Farhan  Handover</t>
-  </si>
-  <si>
-    <t>farhan@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4434</t>
-  </si>
-  <si>
-    <t>Faris</t>
-  </si>
-  <si>
-    <t>faris@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1977</t>
-  </si>
-  <si>
-    <t>09/01/2016</t>
-  </si>
-  <si>
-    <t>Farzin Mohammed  V</t>
-  </si>
-  <si>
-    <t>farzin@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1435</t>
-  </si>
-  <si>
-    <t>Faseela KK</t>
-  </si>
-  <si>
-    <t>faseela@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1463</t>
-  </si>
-  <si>
-    <t>faseela@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP9804</t>
-  </si>
-  <si>
-    <t>Fida  Ashraf O</t>
-  </si>
-  <si>
-    <t>fida@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4221</t>
-  </si>
-  <si>
-    <t>fida@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP2302</t>
-  </si>
-  <si>
-    <t>Abdul Hafeelu</t>
-  </si>
-  <si>
-    <t>hafeelu@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4230</t>
-  </si>
-  <si>
-    <t>Senior Quality Analyst</t>
-  </si>
-  <si>
-    <t>27/11/2025</t>
-  </si>
-  <si>
-    <t>14/02/2002</t>
-  </si>
-  <si>
-    <t>Hafis C P</t>
-  </si>
-  <si>
-    <t>hafis@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3326</t>
-  </si>
-  <si>
-    <t>IOCOD</t>
-  </si>
-  <si>
-    <t>info@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3441</t>
-  </si>
-  <si>
-    <t>Muhammed Jabir C</t>
-  </si>
-  <si>
-    <t>jabir@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3675</t>
-  </si>
-  <si>
-    <t>Muhammed Jasim K</t>
-  </si>
-  <si>
-    <t>jasim@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/ 1040</t>
-  </si>
-  <si>
-    <t>Team Lead</t>
-  </si>
-  <si>
-    <t>Jerish  Edward</t>
-  </si>
-  <si>
-    <t>jerish@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1330</t>
-  </si>
-  <si>
-    <t>Jestina  Thomson</t>
-  </si>
-  <si>
-    <t>jestina@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2286</t>
-  </si>
-  <si>
-    <t>Jinesh KP</t>
-  </si>
-  <si>
-    <t>jinesh@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2015</t>
-  </si>
-  <si>
-    <t>Jishad P</t>
-  </si>
-  <si>
-    <t>jishad@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP7301</t>
-  </si>
-  <si>
-    <t>Jithin A</t>
-  </si>
-  <si>
-    <t>jithin@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4232</t>
-  </si>
-  <si>
-    <t>Keerthana  Murali</t>
-  </si>
-  <si>
-    <t>keerthanamurali@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3409</t>
-  </si>
-  <si>
-    <t>kk.fasil</t>
-  </si>
-  <si>
-    <t>kk.fasil@yahoo.com</t>
-  </si>
-  <si>
-    <t>EMP6579</t>
-  </si>
-  <si>
-    <t>laya@easify.app</t>
-  </si>
-  <si>
-    <t>EMP8549</t>
-  </si>
-  <si>
-    <t>lisak</t>
-  </si>
-  <si>
-    <t>lisak@sbacfunding.com</t>
-  </si>
-  <si>
-    <t>EMP3598</t>
-  </si>
-  <si>
-    <t>mailme</t>
-  </si>
-  <si>
-    <t>mailme@rohitwanchoo.com</t>
-  </si>
-  <si>
-    <t>EMP7089</t>
-  </si>
-  <si>
-    <t>melvin@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP2473</t>
-  </si>
-  <si>
-    <t>Merin  Mohan</t>
-  </si>
-  <si>
-    <t>merin@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP5275</t>
-  </si>
-  <si>
-    <t>Mubashir</t>
-  </si>
-  <si>
-    <t>mubashir@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP7549</t>
-  </si>
-  <si>
-    <t>muhammedshameem880@gmail.com</t>
-  </si>
-  <si>
-    <t>EMP9867</t>
-  </si>
-  <si>
-    <t>Nauf  KG</t>
-  </si>
-  <si>
-    <t>nauf@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP5393</t>
-  </si>
-  <si>
-    <t>Neda Ashraf</t>
-  </si>
-  <si>
-    <t>neda@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2711</t>
-  </si>
-  <si>
-    <t>Neethu k</t>
-  </si>
-  <si>
-    <t>neethu.k@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2509</t>
-  </si>
-  <si>
-    <t>Neethu  Martin</t>
-  </si>
-  <si>
-    <t>neethu@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP8723</t>
-  </si>
-  <si>
-    <t>neethu@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP9485</t>
-  </si>
-  <si>
-    <t>Nejla K P</t>
-  </si>
-  <si>
-    <t>nejla@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1043</t>
-  </si>
-  <si>
-    <t>HR Associate</t>
-  </si>
-  <si>
-    <t>03/11/2021</t>
-  </si>
-  <si>
-    <t>new hr</t>
-  </si>
-  <si>
-    <t>hr</t>
-  </si>
-  <si>
-    <t>Nihal  PP</t>
-  </si>
-  <si>
-    <t>nihal@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3197</t>
-  </si>
-  <si>
-    <t>office</t>
-  </si>
-  <si>
-    <t>office@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3917</t>
-  </si>
-  <si>
-    <t>Patrick Mevis</t>
-  </si>
-  <si>
-    <t>patrick@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP7264</t>
-  </si>
-  <si>
-    <t>Pranav</t>
-  </si>
-  <si>
-    <t>pranav@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2488</t>
-  </si>
-  <si>
-    <t>Priya TP</t>
-  </si>
-  <si>
-    <t>priya@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1349</t>
-  </si>
-  <si>
-    <t>IOCOD TESTING MMP</t>
-  </si>
-  <si>
-    <t>qaiocod@gmail.com</t>
-  </si>
-  <si>
-    <t>EMP5893</t>
-  </si>
-  <si>
-    <t>Raneesa  K</t>
-  </si>
-  <si>
-    <t>raneesa@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3561</t>
-  </si>
-  <si>
-    <t>Muhammed Rashid P</t>
-  </si>
-  <si>
-    <t>rashidp@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP7869</t>
-  </si>
-  <si>
-    <t>rina@easify.app</t>
-  </si>
-  <si>
-    <t>EMP7642</t>
-  </si>
-  <si>
-    <t>Rishab Haridas</t>
-  </si>
-  <si>
-    <t>rishab@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3535</t>
-  </si>
-  <si>
-    <t>Rishana SKP</t>
-  </si>
-  <si>
-    <t>rishana@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6997</t>
-  </si>
-  <si>
-    <t>rishana@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP3046</t>
-  </si>
-  <si>
-    <t>Rohith  K</t>
-  </si>
-  <si>
-    <t>rohith@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1004</t>
-  </si>
-  <si>
-    <t>Sabil K</t>
-  </si>
-  <si>
-    <t>sabil@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4631</t>
-  </si>
-  <si>
-    <t>sagar s kumar</t>
-  </si>
-  <si>
-    <t>sagar@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4896</t>
-  </si>
-  <si>
-    <t>Sahal Muhammed KK</t>
-  </si>
-  <si>
-    <t>sahal@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2846</t>
-  </si>
-  <si>
-    <t>Laravel Developer</t>
-  </si>
-  <si>
-    <t>15/11/2025</t>
-  </si>
-  <si>
-    <t>sales</t>
-  </si>
-  <si>
-    <t>sales@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6636</t>
-  </si>
-  <si>
-    <t>saranya iocod</t>
-  </si>
-  <si>
-    <t>saranya@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4093</t>
-  </si>
-  <si>
-    <t>saranya@zinops.com</t>
-  </si>
-  <si>
-    <t>EMP2137</t>
-  </si>
-  <si>
-    <t>Shahana Sherin</t>
-  </si>
-  <si>
-    <t>shahana@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP5832</t>
-  </si>
-  <si>
-    <t>Muhammed Shaheer P</t>
-  </si>
-  <si>
-    <t>shaheer@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2012</t>
-  </si>
-  <si>
-    <t>shameem@mca.plus</t>
-  </si>
-  <si>
-    <t>EMP8421</t>
-  </si>
-  <si>
-    <t>P Mohamed Shanid</t>
-  </si>
-  <si>
-    <t>shanid@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP9578</t>
-  </si>
-  <si>
-    <t>Sherin  Thomas</t>
-  </si>
-  <si>
-    <t>sherin@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3530</t>
-  </si>
-  <si>
-    <t>Shifana KS</t>
-  </si>
-  <si>
-    <t>shifana@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP1294</t>
-  </si>
-  <si>
-    <t>Sreehari PO</t>
-  </si>
-  <si>
-    <t>sreeharipo@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6974</t>
-  </si>
-  <si>
-    <t>Sreejesh CV</t>
-  </si>
-  <si>
-    <t>sreejeshk@mercantilepacific.com</t>
-  </si>
-  <si>
-    <t>EMP4370</t>
-  </si>
-  <si>
-    <t>Suvidya Raj TM</t>
-  </si>
-  <si>
-    <t>suvidya@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4133</t>
-  </si>
-  <si>
-    <t>Fathima Thamanna  Filsher</t>
-  </si>
-  <si>
-    <t>thamanna@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP6025</t>
-  </si>
-  <si>
-    <t>Uvais Mohammad</t>
-  </si>
-  <si>
-    <t>uvais@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP9981</t>
-  </si>
-  <si>
-    <t>Vijay Mathew</t>
-  </si>
-  <si>
-    <t>vijay@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP4240</t>
-  </si>
-  <si>
-    <t>YASHIN  TM</t>
-  </si>
-  <si>
-    <t>yashin@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP3165</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>Zainab  SH</t>
-  </si>
-  <si>
-    <t>zainab@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP2021</t>
-  </si>
-  <si>
-    <t>HR Manager</t>
-  </si>
-  <si>
-    <t>hr@example.com</t>
-  </si>
-  <si>
-    <t>hr/11</t>
-  </si>
-  <si>
-    <t>15/12/2025</t>
-  </si>
-  <si>
-    <t>PM User</t>
-  </si>
-  <si>
-    <t>pm@example.com</t>
-  </si>
-  <si>
-    <t>pm/11</t>
-  </si>
-  <si>
-    <t>17/12/2025</t>
-  </si>
-  <si>
-    <t>lead@example.com</t>
-  </si>
-  <si>
-    <t>tl/11</t>
-  </si>
-  <si>
-    <t>team-lead</t>
-  </si>
-  <si>
-    <t>Employee User</t>
-  </si>
-  <si>
-    <t>employee@example.com</t>
-  </si>
-  <si>
-    <t>emp/11</t>
-  </si>
-  <si>
-    <t>17/01/2023</t>
-  </si>
-  <si>
-    <t>udemy IOCOD</t>
-  </si>
-  <si>
-    <t>udemy@iocod.com</t>
-  </si>
-  <si>
-    <t>ud1212</t>
-  </si>
-  <si>
-    <t>Olivia Davis</t>
-  </si>
-  <si>
-    <t>olivia@gmail.com</t>
-  </si>
-  <si>
-    <t>emp/132</t>
-  </si>
-  <si>
-    <t>02/01/2022</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>name@gmail.com</t>
-  </si>
-  <si>
-    <t>name1212</t>
-  </si>
-  <si>
-    <t>24/12/2025</t>
-  </si>
-  <si>
-    <t>Abhiram  Santhosh</t>
-  </si>
-  <si>
-    <t>abhiramsanthosh@iocod.com</t>
-  </si>
-  <si>
-    <t>abhiram/11</t>
-  </si>
-  <si>
-    <t>01/11/2025</t>
-  </si>
-  <si>
-    <t>Vaishnav VC</t>
-  </si>
-  <si>
-    <t>Vaishnav@iocod.com</t>
-  </si>
-  <si>
-    <t>emp12</t>
-  </si>
-  <si>
-    <t>Quality Analyst</t>
-  </si>
-  <si>
-    <t>11/12/2025</t>
-  </si>
-  <si>
-    <t>Developer</t>
-  </si>
-  <si>
-    <t>developer@iocod.com</t>
-  </si>
-  <si>
-    <t>emp12121</t>
-  </si>
-  <si>
-    <t>26/12/2025</t>
-  </si>
-  <si>
-    <t>Abhiram Krishna M</t>
-  </si>
-  <si>
-    <t>abhiram@iocod.com</t>
-  </si>
-  <si>
-    <t>Orgnice designation</t>
-  </si>
-  <si>
-    <t>06/01/2026</t>
-  </si>
-  <si>
-    <t>Abhishek M Menon</t>
-  </si>
-  <si>
-    <t>abhishek@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1074</t>
-  </si>
-  <si>
-    <t>Software Developer</t>
-  </si>
-  <si>
-    <t>02/08/2023</t>
-  </si>
-  <si>
-    <t>Adyuth P</t>
-  </si>
-  <si>
-    <t>adyuth@iocod.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMP/IIPL/1063</t>
-  </si>
-  <si>
-    <t>UI/UX Team Lead</t>
-  </si>
-  <si>
-    <t>Muhammed Ahnas K K</t>
-  </si>
-  <si>
-    <t>ahnas@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1016</t>
-  </si>
-  <si>
-    <t>Akash N O</t>
-  </si>
-  <si>
-    <t>akash@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1066</t>
-  </si>
-  <si>
-    <t>15/03/2023</t>
-  </si>
-  <si>
-    <t>Rashid Pathiyil</t>
-  </si>
-  <si>
-    <t>Aleena Joseph</t>
-  </si>
-  <si>
-    <t>aleena@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1122</t>
-  </si>
-  <si>
-    <t>Junior QA Engineer</t>
-  </si>
-  <si>
-    <t>02/07/2024</t>
-  </si>
-  <si>
-    <t>Amaya VS</t>
-  </si>
-  <si>
-    <t>amaya@iocod.com</t>
-  </si>
-  <si>
-    <t>QA Engineer</t>
-  </si>
-  <si>
-    <t>03/12/2025</t>
-  </si>
-  <si>
-    <t>Anagha Ajith</t>
-  </si>
-  <si>
-    <t>anaghaajith@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1143</t>
-  </si>
-  <si>
-    <t>Data Processing Executive</t>
-  </si>
-  <si>
-    <t>17/02/2025</t>
-  </si>
-  <si>
-    <t>Abhijith M</t>
-  </si>
-  <si>
-    <t>Anagha O</t>
-  </si>
-  <si>
-    <t>anaghao@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1076</t>
-  </si>
-  <si>
-    <t>11/08/2023</t>
-  </si>
-  <si>
-    <t>Anandhu Mohanan</t>
-  </si>
-  <si>
-    <t>anandhum@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1142</t>
-  </si>
-  <si>
-    <t>Content Writer</t>
-  </si>
-  <si>
-    <t>10/02/2025</t>
-  </si>
-  <si>
-    <t>Shanosh Kumar TA</t>
-  </si>
-  <si>
-    <t>Anargha G K</t>
-  </si>
-  <si>
-    <t>anargha@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1128</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>Aneesh Paulson M</t>
-  </si>
-  <si>
-    <t>aneesh@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1135</t>
-  </si>
-  <si>
-    <t>Senior Software Developer</t>
-  </si>
-  <si>
-    <t>20/01/2025</t>
-  </si>
-  <si>
-    <t>Fahid Hassan K</t>
-  </si>
-  <si>
-    <t>Anshad P V</t>
-  </si>
-  <si>
-    <t>anshad@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1137</t>
-  </si>
-  <si>
-    <t>03/02/2025</t>
-  </si>
-  <si>
-    <t>Anukrishnan KS</t>
-  </si>
-  <si>
-    <t>anukrishnan@iocod.com</t>
-  </si>
-  <si>
-    <t>Senior Laravel Developer</t>
-  </si>
-  <si>
-    <t>Anurag C K</t>
-  </si>
-  <si>
-    <t>anurag@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1065</t>
-  </si>
-  <si>
-    <t>13/03/2023</t>
-  </si>
-  <si>
-    <t>Anwar Sabith M</t>
-  </si>
-  <si>
-    <t>anwar@iocod.com</t>
-  </si>
-  <si>
-    <t>swfha</t>
-  </si>
-  <si>
-    <t>Arshad Mannilkadavan</t>
-  </si>
-  <si>
-    <t>arshad@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1099</t>
-  </si>
-  <si>
-    <t>UI/UX Designer</t>
-  </si>
-  <si>
-    <t>08/01/2024</t>
-  </si>
-  <si>
-    <t>Mohammad Ashfaqudheen</t>
-  </si>
-  <si>
-    <t>ashfaq@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1079</t>
-  </si>
-  <si>
-    <t>24/08/2023</t>
-  </si>
-  <si>
-    <t>Aswathi Mukundan</t>
-  </si>
-  <si>
-    <t>aswathim@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1098</t>
-  </si>
-  <si>
-    <t>20/12/2023</t>
-  </si>
-  <si>
-    <t>Aswin Vilas P</t>
-  </si>
-  <si>
-    <t>aswin@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1124</t>
-  </si>
-  <si>
-    <t>attendance</t>
-  </si>
-  <si>
-    <t>Attendance@iocod.com</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>Badhsha  K</t>
-  </si>
-  <si>
-    <t>badhsha@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1127</t>
-  </si>
-  <si>
-    <t>Muhammed Basil E</t>
-  </si>
-  <si>
-    <t>basil@iocod.com</t>
-  </si>
-  <si>
-    <t>EMP/IIPL/1051</t>
-  </si>
-  <si>
     <t>Basil Rayees</t>
   </si>
   <si>
@@ -1958,7 +1973,7 @@
     <t>Vimal Johnson</t>
   </si>
   <si>
-    <t>vimal@iocod.com</t>
+    <t>Vimal@iocod.com</t>
   </si>
   <si>
     <t>EMP /IIPL /1081</t>
@@ -2060,7 +2075,7 @@
     <t>EMP/IIPL/1089</t>
   </si>
   <si>
-    <t>15/07/2023</t>
+    <t>05/03/2023</t>
   </si>
   <si>
     <t>Abhijith P</t>
@@ -2072,7 +2087,10 @@
     <t>EMP/IIPL/01018</t>
   </si>
   <si>
-    <t>06/10/2019</t>
+    <t>05/03/2019</t>
+  </si>
+  <si>
+    <t>19/01/2026</t>
   </si>
   <si>
     <t>Abhinav Vinod</t>
@@ -2084,9 +2102,6 @@
     <t>EMP/IIPL/1179</t>
   </si>
   <si>
-    <t>14/02/2025</t>
-  </si>
-  <si>
     <t>15/02/2000</t>
   </si>
   <si>
@@ -2219,7 +2234,58 @@
     <t>jkgkjg</t>
   </si>
   <si>
-    <t>14/02/2023</t>
+    <t>18/02/2003</t>
+  </si>
+  <si>
+    <t>testuser@gmail.com</t>
+  </si>
+  <si>
+    <t>EMP423111</t>
+  </si>
+  <si>
+    <t>25/02/2025</t>
+  </si>
+  <si>
+    <t>new user</t>
+  </si>
+  <si>
+    <t>newuser@gmail.com</t>
+  </si>
+  <si>
+    <t>gexecak135@keevle.com</t>
+  </si>
+  <si>
+    <t>26/02/2025</t>
+  </si>
+  <si>
+    <t>27/02/2025</t>
+  </si>
+  <si>
+    <t>newuser1@gmail.com</t>
+  </si>
+  <si>
+    <t>samad11111@iocod.com</t>
+  </si>
+  <si>
+    <t>05/03/2025</t>
+  </si>
+  <si>
+    <t>aaaa1</t>
+  </si>
+  <si>
+    <t>hafeeluqqq@iocod.com</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>user02</t>
+  </si>
+  <si>
+    <t>user02@gmail.com</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
   </si>
 </sst>
 </file>
@@ -2603,7 +2669,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K207"/>
+  <dimension ref="A1:K213"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="34.135" bestFit="true" customWidth="true" style="0"/>
@@ -2671,27 +2737,29 @@
       <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -2700,67 +2768,76 @@
       <c r="H3" s="5"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -2769,18 +2846,18 @@
       <c r="H6" s="4"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2789,18 +2866,18 @@
       <c r="H7" s="5"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2809,49 +2886,49 @@
       <c r="H8" s="4"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2860,18 +2937,18 @@
       <c r="H10" s="4"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2880,18 +2957,18 @@
       <c r="H11" s="5"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2900,51 +2977,51 @@
       <c r="H12" s="4"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -2953,18 +3030,18 @@
       <c r="H14" s="4"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2973,18 +3050,18 @@
       <c r="H15" s="5"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -2993,18 +3070,18 @@
       <c r="H16" s="4"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -3013,45 +3090,45 @@
       <c r="H17" s="5"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -3060,47 +3137,47 @@
       <c r="H19" s="5"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3109,18 +3186,18 @@
       <c r="H21" s="5"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -3129,43 +3206,43 @@
       <c r="H22" s="4"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -3174,18 +3251,18 @@
       <c r="H24" s="4"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -3194,18 +3271,18 @@
       <c r="H25" s="5"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -3214,18 +3291,18 @@
       <c r="H26" s="4"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -3234,18 +3311,18 @@
       <c r="H27" s="5"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -3254,18 +3331,18 @@
       <c r="H28" s="4"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -3274,45 +3351,45 @@
       <c r="H29" s="5"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -3321,45 +3398,45 @@
       <c r="H31" s="5"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -3368,18 +3445,18 @@
       <c r="H33" s="5"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -3388,18 +3465,18 @@
       <c r="H34" s="4"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -3408,18 +3485,18 @@
       <c r="H35" s="5"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -3428,18 +3505,18 @@
       <c r="H36" s="4"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -3448,51 +3525,51 @@
       <c r="H37" s="5"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -3501,18 +3578,18 @@
       <c r="H39" s="5"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -3521,18 +3598,18 @@
       <c r="H40" s="4"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -3541,40 +3618,40 @@
       <c r="H41" s="5"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -3583,18 +3660,18 @@
       <c r="H43" s="5"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3603,18 +3680,18 @@
       <c r="H44" s="4"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -3623,40 +3700,40 @@
       <c r="H45" s="5"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -3665,18 +3742,18 @@
       <c r="H47" s="5"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3685,18 +3762,18 @@
       <c r="H48" s="4"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -3705,18 +3782,18 @@
       <c r="H49" s="5"/>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -3725,18 +3802,18 @@
       <c r="H50" s="4"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -3745,18 +3822,18 @@
       <c r="H51" s="5"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -3765,18 +3842,18 @@
       <c r="H52" s="4"/>
       <c r="I52" s="6"/>
       <c r="J52" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -3785,18 +3862,18 @@
       <c r="H53" s="5"/>
       <c r="I53" s="7"/>
       <c r="J53" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -3805,18 +3882,18 @@
       <c r="H54" s="4"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -3825,18 +3902,18 @@
       <c r="H55" s="5"/>
       <c r="I55" s="7"/>
       <c r="J55" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3845,18 +3922,18 @@
       <c r="H56" s="4"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -3865,18 +3942,18 @@
       <c r="H57" s="5"/>
       <c r="I57" s="7"/>
       <c r="J57" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -3885,18 +3962,18 @@
       <c r="H58" s="4"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -3905,18 +3982,18 @@
       <c r="H59" s="5"/>
       <c r="I59" s="7"/>
       <c r="J59" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -3925,18 +4002,18 @@
       <c r="H60" s="4"/>
       <c r="I60" s="6"/>
       <c r="J60" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -3945,49 +4022,49 @@
       <c r="H61" s="5"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K62" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -3996,18 +4073,18 @@
       <c r="H63" s="5"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -4016,18 +4093,18 @@
       <c r="H64" s="4"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
@@ -4036,18 +4113,18 @@
       <c r="H65" s="5"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -4056,18 +4133,18 @@
       <c r="H66" s="4"/>
       <c r="I66" s="6"/>
       <c r="J66" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -4076,18 +4153,18 @@
       <c r="H67" s="5"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -4096,18 +4173,18 @@
       <c r="H68" s="4"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -4116,18 +4193,18 @@
       <c r="H69" s="5"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -4136,18 +4213,18 @@
       <c r="H70" s="4"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -4156,18 +4233,18 @@
       <c r="H71" s="5"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -4176,18 +4253,18 @@
       <c r="H72" s="4"/>
       <c r="I72" s="6"/>
       <c r="J72" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -4196,18 +4273,18 @@
       <c r="H73" s="5"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -4216,18 +4293,18 @@
       <c r="H74" s="4"/>
       <c r="I74" s="6"/>
       <c r="J74" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -4236,18 +4313,18 @@
       <c r="H75" s="5"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -4256,18 +4333,18 @@
       <c r="H76" s="4"/>
       <c r="I76" s="6"/>
       <c r="J76" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -4276,47 +4353,47 @@
       <c r="H77" s="5"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K78" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -4325,18 +4402,18 @@
       <c r="H79" s="5"/>
       <c r="I79" s="7"/>
       <c r="J79" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -4345,18 +4422,18 @@
       <c r="H80" s="4"/>
       <c r="I80" s="6"/>
       <c r="J80" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -4365,18 +4442,18 @@
       <c r="H81" s="5"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -4385,18 +4462,18 @@
       <c r="H82" s="4"/>
       <c r="I82" s="6"/>
       <c r="J82" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -4405,18 +4482,18 @@
       <c r="H83" s="5"/>
       <c r="I83" s="7"/>
       <c r="J83" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -4425,18 +4502,18 @@
       <c r="H84" s="4"/>
       <c r="I84" s="6"/>
       <c r="J84" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -4445,18 +4522,18 @@
       <c r="H85" s="5"/>
       <c r="I85" s="7"/>
       <c r="J85" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -4465,18 +4542,18 @@
       <c r="H86" s="4"/>
       <c r="I86" s="6"/>
       <c r="J86" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -4485,18 +4562,18 @@
       <c r="H87" s="5"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -4505,18 +4582,18 @@
       <c r="H88" s="4"/>
       <c r="I88" s="6"/>
       <c r="J88" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -4525,18 +4602,18 @@
       <c r="H89" s="5"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -4545,18 +4622,18 @@
       <c r="H90" s="4"/>
       <c r="I90" s="6"/>
       <c r="J90" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -4565,18 +4642,18 @@
       <c r="H91" s="5"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -4585,18 +4662,18 @@
       <c r="H92" s="4"/>
       <c r="I92" s="6"/>
       <c r="J92" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -4605,49 +4682,49 @@
       <c r="H93" s="5"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -4656,1073 +4733,1084 @@
       <c r="H95" s="5"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K96" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K97" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K98" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K99" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K100" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K101" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K102" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="G103" s="5"/>
+        <v>345</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>346</v>
+      </c>
       <c r="H103" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K103" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K104" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K105" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C106" s="4">
         <v>2341</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G106" s="4"/>
+        <v>346</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>359</v>
+      </c>
       <c r="H106" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K106" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>60</v>
+        <v>365</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K107" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
+        <v>369</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>370</v>
+      </c>
       <c r="H108" s="4"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K108" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="4" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D110" s="4"/>
       <c r="E110" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K110" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="5" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="5" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K111" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="4" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K112" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="5" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K113" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K114" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="5" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K115" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F116" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H116" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="G116" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>398</v>
-      </c>
       <c r="I116" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K116" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K117" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K118" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K120" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="5" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D121" s="5"/>
       <c r="E121" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I121" s="7"/>
       <c r="J121" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K121" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K122" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="5" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D123" s="5"/>
       <c r="E123" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K123" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K124" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D125" s="5"/>
       <c r="E125" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="7"/>
       <c r="J125" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K125" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="6"/>
       <c r="J126" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D127" s="5"/>
       <c r="E127" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="7"/>
       <c r="J127" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4" t="s">
-        <v>26</v>
+        <v>452</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
       <c r="I128" s="6"/>
       <c r="J128" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="5" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D129" s="5"/>
       <c r="E129" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K129" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K130" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D131" s="5"/>
       <c r="E131" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K131" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="4" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -5732,374 +5820,374 @@
       <c r="H132" s="4"/>
       <c r="I132" s="6"/>
       <c r="J132" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="5" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D133" s="5"/>
       <c r="E133" s="5" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K133" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="5" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="7"/>
       <c r="J135" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="6"/>
       <c r="J136" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="5" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="5" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="I137" s="7"/>
       <c r="J137" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K137" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
       <c r="I138" s="6"/>
       <c r="J138" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K138" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="5" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D139" s="5"/>
       <c r="E139" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K139" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="4" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K140" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="5" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="5" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="7"/>
       <c r="J141" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K142" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="5" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="7"/>
       <c r="J143" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="4" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J144" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K144" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="5" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="7"/>
       <c r="J145" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="4" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
       <c r="I146" s="6"/>
       <c r="J146" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="5" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
@@ -6109,857 +6197,857 @@
       <c r="H147" s="5"/>
       <c r="I147" s="7"/>
       <c r="J147" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K148" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="5" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="5" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
       <c r="I149" s="7"/>
       <c r="J149" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K150" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="5" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D151" s="5"/>
       <c r="E151" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="7"/>
       <c r="J151" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="4" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J152" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K152" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="5" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D153" s="5"/>
       <c r="E153" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K153" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="4" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J154" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K154" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="5" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D155" s="5"/>
       <c r="E155" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K155" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="4" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="G156" s="4"/>
       <c r="H156" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K156" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="5" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="4" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="G158" s="4"/>
       <c r="H158" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K158" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="5" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D159" s="5"/>
       <c r="E159" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
       <c r="I159" s="7"/>
       <c r="J159" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="4" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
       <c r="I160" s="6"/>
       <c r="J160" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="5" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D161" s="5"/>
       <c r="E161" s="5" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K161" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="6"/>
       <c r="J162" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="5" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D163" s="5"/>
       <c r="E163" s="5" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K163" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="G164" s="4"/>
       <c r="H164" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K164" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="5" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D165" s="5"/>
       <c r="E165" s="5" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="G165" s="5"/>
       <c r="H165" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K165" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="4" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G166" s="4"/>
       <c r="H166" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K166" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="5" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D167" s="5"/>
       <c r="E167" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="4" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="G168" s="4"/>
       <c r="H168" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J168" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K168" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="5" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D169" s="5"/>
       <c r="E169" s="5" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
       <c r="H169" s="5"/>
       <c r="I169" s="7"/>
       <c r="J169" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="4" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
       <c r="I170" s="6"/>
       <c r="J170" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="5" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K171" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="6"/>
       <c r="J172" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="5" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="5" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="F173" s="5"/>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="7"/>
       <c r="J173" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="4" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="G174" s="4"/>
       <c r="H174" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K174" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="5" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D175" s="5"/>
       <c r="E175" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K175" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="4" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="G176" s="4"/>
       <c r="H176" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J176" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K176" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="5" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F177" s="5"/>
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="I177" s="7"/>
       <c r="J177" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="4" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="6"/>
       <c r="J178" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="5" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
@@ -6969,46 +7057,46 @@
       <c r="H179" s="5"/>
       <c r="I179" s="7"/>
       <c r="J179" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="4" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G180" s="4"/>
       <c r="H180" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K180" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="5" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
@@ -7018,811 +7106,1007 @@
       <c r="H181" s="5"/>
       <c r="I181" s="7"/>
       <c r="J181" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="4" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="G182" s="4"/>
       <c r="H182" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K182" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="5" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F183" s="5"/>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="7"/>
       <c r="J183" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="4" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
       <c r="I184" s="6"/>
       <c r="J184" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="G185" s="5"/>
       <c r="H185" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I185" s="7"/>
       <c r="J185" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K185" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J186" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K186" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="5" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D187" s="5"/>
       <c r="E187" s="5" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G187" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="H187" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J187" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K187" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="G188" s="4"/>
       <c r="H188" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K188" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="5" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C189" s="5">
         <v>12355</v>
       </c>
       <c r="D189" s="5"/>
       <c r="E189" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="G189" s="5"/>
       <c r="H189" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J189" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K189" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="G190" s="4"/>
       <c r="H190" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I190" s="6"/>
       <c r="J190" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K190" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="5" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D191" s="5"/>
       <c r="E191" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="G191" s="5"/>
       <c r="H191" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I191" s="7"/>
       <c r="J191" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K191" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C192" s="4">
         <v>7676</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="G192" s="4"/>
       <c r="H192" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J192" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K192" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D193" s="5"/>
       <c r="E193" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>142</v>
+        <v>365</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K193" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="4" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>60</v>
+        <v>691</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J194" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K194" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="5" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D195" s="5"/>
       <c r="E195" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>689</v>
+        <v>370</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K195" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="4" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C196" s="4">
         <v>36363</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="G196" s="4"/>
       <c r="H196" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K196" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="C197" s="5">
         <v>121212121</v>
       </c>
       <c r="D197" s="5"/>
       <c r="E197" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="G197" s="5"/>
       <c r="H197" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K197" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="4" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J198" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K198" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="5" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C199" s="5">
         <v>111111111111</v>
       </c>
       <c r="D199" s="5"/>
       <c r="E199" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K199" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="4" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J200" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K200" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F201" s="5" t="s">
         <v>707</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>702</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K201" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="4" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J202" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K202" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="5" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K203" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="4" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J204" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K204" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="5" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G205" s="5"/>
       <c r="H205" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J205" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K205" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="4" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J206" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K206" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="5" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="H207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J207" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K207" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="H208" s="4" t="s">
         <v>29</v>
+      </c>
+      <c r="I208" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J208" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K208" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11">
+      <c r="A209" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C209" s="5">
+        <v>7878787</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="G209" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="H209" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I209" s="7"/>
+      <c r="J209" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K209" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C210" s="4">
+        <v>12121</v>
+      </c>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I210" s="6"/>
+      <c r="J210" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K210" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" s="5">
+        <v>11111</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="C211" s="5">
+        <v>11111</v>
+      </c>
+      <c r="D211" s="5"/>
+      <c r="E211" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="G211" s="5"/>
+      <c r="H211" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J211" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K211" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="A212" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="C212" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D212" s="4"/>
+      <c r="E212" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="I212" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J212" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K212" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="C213" s="5">
+        <v>121233</v>
+      </c>
+      <c r="D213" s="5"/>
+      <c r="E213" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="H213" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J213" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K213" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/temp_users_file.xlsx
+++ b/temp_users_file.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="927">
   <si>
     <t>Name</t>
   </si>
@@ -65,7 +65,10 @@
     <t>18/02/2022</t>
   </si>
   <si>
-    <t>16/02/2026</t>
+    <t>15/02/2026</t>
+  </si>
+  <si>
+    <t>Fasil KK</t>
   </si>
   <si>
     <t>On-site</t>
@@ -101,12 +104,18 @@
     <t>Software Engineer</t>
   </si>
   <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
     <t>18/02/2025</t>
   </si>
   <si>
     <t>Team Lead User</t>
   </si>
   <si>
+    <t>WFH</t>
+  </si>
+  <si>
     <t>employee</t>
   </si>
   <si>
@@ -194,7 +203,7 @@
     <t>EMP/IIPL/1126</t>
   </si>
   <si>
-    <t>Project Manager</t>
+    <t>Project Manager11</t>
   </si>
   <si>
     <t>18/10/2024</t>
@@ -281,9 +290,6 @@
     <t>31/12/2025</t>
   </si>
   <si>
-    <t>WFH</t>
-  </si>
-  <si>
     <t>biby@mca.plus</t>
   </si>
   <si>
@@ -446,7 +452,7 @@
     <t>Senior Quality Analyst</t>
   </si>
   <si>
-    <t>06/03/2025</t>
+    <t>18/03/2025</t>
   </si>
   <si>
     <t>05/03/2002</t>
@@ -650,7 +656,7 @@
     <t>EMP9485</t>
   </si>
   <si>
-    <t>Nejla K P</t>
+    <t>Nejla K.P</t>
   </si>
   <si>
     <t>nejla@iocod.com</t>
@@ -965,6 +971,12 @@
     <t>EMP2021</t>
   </si>
   <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
+    <t>Abhijith M</t>
+  </si>
+  <si>
     <t>HR Manager</t>
   </si>
   <si>
@@ -995,6 +1007,9 @@
     <t>tl/11</t>
   </si>
   <si>
+    <t>01/01/2001</t>
+  </si>
+  <si>
     <t>team-lead</t>
   </si>
   <si>
@@ -1007,9 +1022,6 @@
     <t>emp/11</t>
   </si>
   <si>
-    <t>17/01/2023</t>
-  </si>
-  <si>
     <t>udemy IOCOD</t>
   </si>
   <si>
@@ -1028,7 +1040,10 @@
     <t>emp/132</t>
   </si>
   <si>
-    <t>02/01/2022</t>
+    <t>Data Processing Executive</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
   </si>
   <si>
     <t>name</t>
@@ -1190,15 +1205,9 @@
     <t>EMP/IIPL/1143</t>
   </si>
   <si>
-    <t>Data Processing Executive</t>
-  </si>
-  <si>
     <t>17/02/2025</t>
   </si>
   <si>
-    <t>Abhijith M</t>
-  </si>
-  <si>
     <t>Anagha O</t>
   </si>
   <si>
@@ -1469,9 +1478,6 @@
     <t>Sr. Software Developer</t>
   </si>
   <si>
-    <t>Fasil KK</t>
-  </si>
-  <si>
     <t>fasil@iocod.com</t>
   </si>
   <si>
@@ -1973,7 +1979,7 @@
     <t>Vimal Johnson</t>
   </si>
   <si>
-    <t>Vimal@iocod.com</t>
+    <t>vimal@iocod.com</t>
   </si>
   <si>
     <t>EMP /IIPL /1081</t>
@@ -2003,6 +2009,9 @@
     <t>renyro@mailinator.com</t>
   </si>
   <si>
+    <t>Junior Front End Developer</t>
+  </si>
+  <si>
     <t>06/12/1996</t>
   </si>
   <si>
@@ -2078,6 +2087,9 @@
     <t>05/03/2023</t>
   </si>
   <si>
+    <t>17/03/2002</t>
+  </si>
+  <si>
     <t>Abhijith P</t>
   </si>
   <si>
@@ -2189,6 +2201,9 @@
     <t>ZjlBu@gmail.com</t>
   </si>
   <si>
+    <t>very long designation name for the testing purpose manual and automation</t>
+  </si>
+  <si>
     <t>AutoUser_dvObA</t>
   </si>
   <si>
@@ -2267,7 +2282,10 @@
     <t>samad11111@iocod.com</t>
   </si>
   <si>
-    <t>05/03/2025</t>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>12/03/2025</t>
   </si>
   <si>
     <t>aaaa1</t>
@@ -2276,7 +2294,7 @@
     <t>hafeeluqqq@iocod.com</t>
   </si>
   <si>
-    <t>25/02/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>user02</t>
@@ -2286,6 +2304,498 @@
   </si>
   <si>
     <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>aneeta</t>
+  </si>
+  <si>
+    <t>aneeta@gmail.com</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>new role for review</t>
+  </si>
+  <si>
+    <t>KALUVALA LAVANYA</t>
+  </si>
+  <si>
+    <t>lavanya@iocod.com</t>
+  </si>
+  <si>
+    <t>gdfgd@tertr.fhf</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>Swathi</t>
+  </si>
+  <si>
+    <t>swathi@iocod.com</t>
+  </si>
+  <si>
+    <t>swathi@gmail.com</t>
+  </si>
+  <si>
+    <t>05/06/2026</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>anju</t>
+  </si>
+  <si>
+    <t>anju@iocod.com</t>
+  </si>
+  <si>
+    <t>anju12</t>
+  </si>
+  <si>
+    <t>09/06/2026</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>sanika</t>
+  </si>
+  <si>
+    <t>sanika@iocod.com</t>
+  </si>
+  <si>
+    <t>san12</t>
+  </si>
+  <si>
+    <t>Amrutha</t>
+  </si>
+  <si>
+    <t>amruthaqa@iocod.com</t>
+  </si>
+  <si>
+    <t>amruthqa2002@gmail.com</t>
+  </si>
+  <si>
+    <t>yashin manoj</t>
+  </si>
+  <si>
+    <t>yashin+2@iocod.com</t>
+  </si>
+  <si>
+    <t>yashin@gmail.com</t>
+  </si>
+  <si>
+    <t>10/06/2026</t>
+  </si>
+  <si>
+    <t>07/12/2002</t>
+  </si>
+  <si>
+    <t>Aneeta</t>
+  </si>
+  <si>
+    <t>aneeta@iocod.com</t>
+  </si>
+  <si>
+    <t>19/10/2000</t>
+  </si>
+  <si>
+    <t>Anupama</t>
+  </si>
+  <si>
+    <t>anu@iocod.com</t>
+  </si>
+  <si>
+    <t>anu@gmail.com</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>01/06/1988</t>
+  </si>
+  <si>
+    <t>Popy Shivakant Dixit</t>
+  </si>
+  <si>
+    <t>popy@iocod.com</t>
+  </si>
+  <si>
+    <t>popy@gmail.com</t>
+  </si>
+  <si>
+    <t>01/01/2005</t>
+  </si>
+  <si>
+    <t>Nikhil Pushpa Maruti</t>
+  </si>
+  <si>
+    <t>nikhil@iocod.com</t>
+  </si>
+  <si>
+    <t>nikhil@gmail.com</t>
+  </si>
+  <si>
+    <t>02/10/2001</t>
+  </si>
+  <si>
+    <t>anu</t>
+  </si>
+  <si>
+    <t>anu1@iocod.com</t>
+  </si>
+  <si>
+    <t>anu1@gmail.com</t>
+  </si>
+  <si>
+    <t>Roshan Pandey</t>
+  </si>
+  <si>
+    <t>roshan@iocod.com</t>
+  </si>
+  <si>
+    <t>john@gmail.com</t>
+  </si>
+  <si>
+    <t>03/01/1995</t>
+  </si>
+  <si>
+    <t>sdvssd</t>
+  </si>
+  <si>
+    <t>samadssss@iocod.com</t>
+  </si>
+  <si>
+    <t>sdasdsdfs</t>
+  </si>
+  <si>
+    <t>16/06/2026</t>
+  </si>
+  <si>
+    <t>Anjana Anil</t>
+  </si>
+  <si>
+    <t>anjana@iocod.com</t>
+  </si>
+  <si>
+    <t>Emily Johnson</t>
+  </si>
+  <si>
+    <t>emily@iocod.com</t>
+  </si>
+  <si>
+    <t>01/03/2025</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>alan@iocod.com</t>
+  </si>
+  <si>
+    <t>alan@gmail.com</t>
+  </si>
+  <si>
+    <t>17/06/2026</t>
+  </si>
+  <si>
+    <t>12/07/2002</t>
+  </si>
+  <si>
+    <t>Nithya</t>
+  </si>
+  <si>
+    <t>nithya@iocod.com</t>
+  </si>
+  <si>
+    <t>nithya@gmail.com</t>
+  </si>
+  <si>
+    <t>23/06/2026</t>
+  </si>
+  <si>
+    <t>01/01/2003</t>
+  </si>
+  <si>
+    <t>Roshan Pandeyuuu</t>
+  </si>
+  <si>
+    <t>sdfgsd@sdfhsdfgh</t>
+  </si>
+  <si>
+    <t>dfgds@dfghdfgh</t>
+  </si>
+  <si>
+    <t>Zain</t>
+  </si>
+  <si>
+    <t>zain@iocod.com</t>
+  </si>
+  <si>
+    <t>zain123</t>
+  </si>
+  <si>
+    <t>25/06/2026</t>
+  </si>
+  <si>
+    <t>01/06/1995</t>
+  </si>
+  <si>
+    <t>malik</t>
+  </si>
+  <si>
+    <t>malik@iocod.com</t>
+  </si>
+  <si>
+    <t>mal123</t>
+  </si>
+  <si>
+    <t>24/06/2026</t>
+  </si>
+  <si>
+    <t>Dia</t>
+  </si>
+  <si>
+    <t>dia@iocod.com</t>
+  </si>
+  <si>
+    <t>dia@gmail.com</t>
+  </si>
+  <si>
+    <t>01/01/1995</t>
+  </si>
+  <si>
+    <t>dilna</t>
+  </si>
+  <si>
+    <t>dilna@iocod.com</t>
+  </si>
+  <si>
+    <t>dil123</t>
+  </si>
+  <si>
+    <t>Sarika</t>
+  </si>
+  <si>
+    <t>sarika@iocod.com</t>
+  </si>
+  <si>
+    <t>sarika@gmail.com</t>
+  </si>
+  <si>
+    <t>16/09/2003</t>
+  </si>
+  <si>
+    <t>Johny</t>
+  </si>
+  <si>
+    <t>johny@iocod.com</t>
+  </si>
+  <si>
+    <t>johny@gmail.com</t>
+  </si>
+  <si>
+    <t>joseph</t>
+  </si>
+  <si>
+    <t>joseph@iocod.com</t>
+  </si>
+  <si>
+    <t>joseph@gmail.com</t>
+  </si>
+  <si>
+    <t>02/07/2026</t>
+  </si>
+  <si>
+    <t>14/12/2004</t>
+  </si>
+  <si>
+    <t>James A</t>
+  </si>
+  <si>
+    <t>james@iocod.com</t>
+  </si>
+  <si>
+    <t>james@gmail.com</t>
+  </si>
+  <si>
+    <t>Emma Taylor</t>
+  </si>
+  <si>
+    <t>emma@iocod.com</t>
+  </si>
+  <si>
+    <t>emma@gmail.com</t>
+  </si>
+  <si>
+    <t>saaraah</t>
+  </si>
+  <si>
+    <t>sarah@iocod.com</t>
+  </si>
+  <si>
+    <t>sarah@gmail.com</t>
+  </si>
+  <si>
+    <t>Emma dani</t>
+  </si>
+  <si>
+    <t>emmadani@iocod.com</t>
+  </si>
+  <si>
+    <t>emmadani@gmail.com</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>Jamiee</t>
+  </si>
+  <si>
+    <t>Jamie@iocod.com</t>
+  </si>
+  <si>
+    <t>jamie@gmail.com</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>Somu</t>
+  </si>
+  <si>
+    <t>somu@iocod.com</t>
+  </si>
+  <si>
+    <t>somu@gmail.com</t>
+  </si>
+  <si>
+    <t>18/07/2026</t>
+  </si>
+  <si>
+    <t>Sojan</t>
+  </si>
+  <si>
+    <t>sojan@iocod.com</t>
+  </si>
+  <si>
+    <t>sojan@gmail.com</t>
+  </si>
+  <si>
+    <t>21/07/2026</t>
+  </si>
+  <si>
+    <t>Panku</t>
+  </si>
+  <si>
+    <t>panku@iocod.com</t>
+  </si>
+  <si>
+    <t>panku@gmail.com</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>Joby</t>
+  </si>
+  <si>
+    <t>joby@iocod.com</t>
+  </si>
+  <si>
+    <t>jobu@gmail.com</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>david@iocod.com</t>
+  </si>
+  <si>
+    <t>IMP001133</t>
+  </si>
+  <si>
+    <t>david@gmail.com</t>
+  </si>
+  <si>
+    <t>10/08/2024</t>
+  </si>
+  <si>
+    <t>01/01/2000</t>
+  </si>
+  <si>
+    <t>JIJI</t>
+  </si>
+  <si>
+    <t>jiji@iocod.com</t>
+  </si>
+  <si>
+    <t>jiji@gmail.com</t>
+  </si>
+  <si>
+    <t>13/08/2026</t>
+  </si>
+  <si>
+    <t>JOJO</t>
+  </si>
+  <si>
+    <t>jojo@iocod.com</t>
+  </si>
+  <si>
+    <t>jojo@gmail.com</t>
+  </si>
+  <si>
+    <t>lijo</t>
+  </si>
+  <si>
+    <t>lijo@iocod.com</t>
+  </si>
+  <si>
+    <t>hgfjhg1111</t>
+  </si>
+  <si>
+    <t>lijo1@gmail.com</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>madu</t>
+  </si>
+  <si>
+    <t>madu@iocod.com</t>
+  </si>
+  <si>
+    <t>emp0988</t>
+  </si>
+  <si>
+    <t>madu@gmail.com</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>charlotte@iocod.com</t>
+  </si>
+  <si>
+    <t>emp/1212</t>
+  </si>
+  <si>
+    <t>charlotte@gmail.com</t>
+  </si>
+  <si>
+    <t>02/02/2002</t>
   </si>
 </sst>
 </file>
@@ -2669,20 +3179,20 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K213"/>
+  <dimension ref="A1:K254"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="34.135" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="37.705" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="47.131" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="85.979" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="22.852" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="20.281" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="20.281" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customHeight="1" ht="25" s="3" customFormat="1">
@@ -2740,26 +3250,28 @@
       <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -2768,76 +3280,78 @@
       <c r="H3" s="5"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="6"/>
+        <v>31</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="J4" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -2846,18 +3360,18 @@
       <c r="H6" s="4"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2866,18 +3380,18 @@
       <c r="H7" s="5"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2886,49 +3400,49 @@
       <c r="H8" s="4"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2937,18 +3451,18 @@
       <c r="H10" s="4"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2957,18 +3471,18 @@
       <c r="H11" s="5"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2977,51 +3491,51 @@
       <c r="H12" s="4"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -3030,18 +3544,18 @@
       <c r="H14" s="4"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -3050,18 +3564,18 @@
       <c r="H15" s="5"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -3070,18 +3584,18 @@
       <c r="H16" s="4"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -3090,45 +3604,45 @@
       <c r="H17" s="5"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -3137,47 +3651,47 @@
       <c r="H19" s="5"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3186,18 +3700,18 @@
       <c r="H21" s="5"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -3206,43 +3720,43 @@
       <c r="H22" s="4"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -3251,18 +3765,18 @@
       <c r="H24" s="4"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -3271,18 +3785,18 @@
       <c r="H25" s="5"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -3291,18 +3805,18 @@
       <c r="H26" s="4"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -3311,18 +3825,18 @@
       <c r="H27" s="5"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -3331,18 +3845,18 @@
       <c r="H28" s="4"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -3351,45 +3865,45 @@
       <c r="H29" s="5"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K30" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -3398,45 +3912,45 @@
       <c r="H31" s="5"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K32" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -3445,18 +3959,18 @@
       <c r="H33" s="5"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -3465,18 +3979,18 @@
       <c r="H34" s="4"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -3485,18 +3999,18 @@
       <c r="H35" s="5"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -3505,18 +4019,18 @@
       <c r="H36" s="4"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -3525,51 +4039,51 @@
       <c r="H37" s="5"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -3578,18 +4092,18 @@
       <c r="H39" s="5"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -3598,18 +4112,18 @@
       <c r="H40" s="4"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -3618,40 +4132,40 @@
       <c r="H41" s="5"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -3660,18 +4174,18 @@
       <c r="H43" s="5"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3680,18 +4194,18 @@
       <c r="H44" s="4"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -3700,40 +4214,40 @@
       <c r="H45" s="5"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -3742,18 +4256,18 @@
       <c r="H47" s="5"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3762,18 +4276,18 @@
       <c r="H48" s="4"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -3782,18 +4296,18 @@
       <c r="H49" s="5"/>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -3802,18 +4316,18 @@
       <c r="H50" s="4"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -3822,18 +4336,18 @@
       <c r="H51" s="5"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -3842,18 +4356,18 @@
       <c r="H52" s="4"/>
       <c r="I52" s="6"/>
       <c r="J52" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -3862,18 +4376,18 @@
       <c r="H53" s="5"/>
       <c r="I53" s="7"/>
       <c r="J53" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -3882,18 +4396,18 @@
       <c r="H54" s="4"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -3902,18 +4416,18 @@
       <c r="H55" s="5"/>
       <c r="I55" s="7"/>
       <c r="J55" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3922,18 +4436,18 @@
       <c r="H56" s="4"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -3942,18 +4456,18 @@
       <c r="H57" s="5"/>
       <c r="I57" s="7"/>
       <c r="J57" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -3962,18 +4476,18 @@
       <c r="H58" s="4"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -3982,18 +4496,18 @@
       <c r="H59" s="5"/>
       <c r="I59" s="7"/>
       <c r="J59" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -4002,18 +4516,18 @@
       <c r="H60" s="4"/>
       <c r="I60" s="6"/>
       <c r="J60" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -4022,49 +4536,49 @@
       <c r="H61" s="5"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K62" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -4073,18 +4587,18 @@
       <c r="H63" s="5"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -4093,18 +4607,18 @@
       <c r="H64" s="4"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
@@ -4113,18 +4627,18 @@
       <c r="H65" s="5"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -4133,18 +4647,18 @@
       <c r="H66" s="4"/>
       <c r="I66" s="6"/>
       <c r="J66" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -4153,18 +4667,18 @@
       <c r="H67" s="5"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -4173,18 +4687,18 @@
       <c r="H68" s="4"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -4193,18 +4707,18 @@
       <c r="H69" s="5"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -4213,18 +4727,18 @@
       <c r="H70" s="4"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -4233,18 +4747,18 @@
       <c r="H71" s="5"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -4253,18 +4767,18 @@
       <c r="H72" s="4"/>
       <c r="I72" s="6"/>
       <c r="J72" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -4273,18 +4787,18 @@
       <c r="H73" s="5"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -4293,18 +4807,18 @@
       <c r="H74" s="4"/>
       <c r="I74" s="6"/>
       <c r="J74" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -4313,18 +4827,18 @@
       <c r="H75" s="5"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -4333,18 +4847,18 @@
       <c r="H76" s="4"/>
       <c r="I76" s="6"/>
       <c r="J76" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -4353,47 +4867,47 @@
       <c r="H77" s="5"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K78" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -4402,18 +4916,18 @@
       <c r="H79" s="5"/>
       <c r="I79" s="7"/>
       <c r="J79" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -4422,18 +4936,18 @@
       <c r="H80" s="4"/>
       <c r="I80" s="6"/>
       <c r="J80" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -4442,18 +4956,18 @@
       <c r="H81" s="5"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -4462,18 +4976,18 @@
       <c r="H82" s="4"/>
       <c r="I82" s="6"/>
       <c r="J82" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -4482,18 +4996,18 @@
       <c r="H83" s="5"/>
       <c r="I83" s="7"/>
       <c r="J83" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -4502,18 +5016,18 @@
       <c r="H84" s="4"/>
       <c r="I84" s="6"/>
       <c r="J84" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -4522,18 +5036,18 @@
       <c r="H85" s="5"/>
       <c r="I85" s="7"/>
       <c r="J85" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -4542,18 +5056,18 @@
       <c r="H86" s="4"/>
       <c r="I86" s="6"/>
       <c r="J86" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -4562,18 +5076,18 @@
       <c r="H87" s="5"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -4582,18 +5096,18 @@
       <c r="H88" s="4"/>
       <c r="I88" s="6"/>
       <c r="J88" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -4602,18 +5116,18 @@
       <c r="H89" s="5"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -4622,18 +5136,18 @@
       <c r="H90" s="4"/>
       <c r="I90" s="6"/>
       <c r="J90" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -4642,18 +5156,18 @@
       <c r="H91" s="5"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -4662,18 +5176,18 @@
       <c r="H92" s="4"/>
       <c r="I92" s="6"/>
       <c r="J92" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -4682,1135 +5196,1146 @@
       <c r="H93" s="5"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K94" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
+      <c r="E95" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>318</v>
+      </c>
       <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
+      <c r="H95" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="K95" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K96" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K97" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G98" s="4"/>
+        <v>327</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>330</v>
+      </c>
       <c r="H98" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K98" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>330</v>
+        <v>99</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K99" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K100" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="5" t="s">
-        <v>27</v>
+        <v>341</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K101" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="4" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K102" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="5" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K103" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K104" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K105" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="4" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C106" s="4">
         <v>2341</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K106" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K107" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K108" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="5" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="4" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D110" s="4"/>
       <c r="E110" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K110" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="5" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K111" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="4" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K112" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="5" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K113" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K114" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K115" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="4" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K116" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="5" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K117" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="4" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K118" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="5" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K120" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="5" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D121" s="5"/>
       <c r="E121" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I121" s="7"/>
       <c r="J121" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K121" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K122" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D123" s="5"/>
       <c r="E123" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K123" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K124" t="s">
-        <v>30</v>
+        <v>331</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="5" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D125" s="5"/>
       <c r="E125" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="7"/>
       <c r="J125" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K125" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="4" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="6"/>
       <c r="J126" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D127" s="5"/>
       <c r="E127" s="5" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="7"/>
       <c r="J127" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="4" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
       <c r="I128" s="6"/>
       <c r="J128" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D129" s="5"/>
       <c r="E129" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K129" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="4" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K130" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="5" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D131" s="5"/>
       <c r="E131" s="5" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K131" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="4" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -5820,374 +6345,374 @@
       <c r="H132" s="4"/>
       <c r="I132" s="6"/>
       <c r="J132" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="5" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D133" s="5"/>
       <c r="E133" s="5" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K133" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="4" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="7"/>
       <c r="J135" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="6"/>
       <c r="J136" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="5" t="s">
-        <v>484</v>
+        <v>17</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="I137" s="7"/>
       <c r="J137" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K137" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
       <c r="I138" s="6"/>
       <c r="J138" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K138" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D139" s="5"/>
       <c r="E139" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K139" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K140" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="5" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="7"/>
       <c r="J141" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K142" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="5" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="7"/>
       <c r="J143" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J144" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K144" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="5" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="7"/>
       <c r="J145" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="4" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
       <c r="I146" s="6"/>
       <c r="J146" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="5" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
@@ -6197,857 +6722,862 @@
       <c r="H147" s="5"/>
       <c r="I147" s="7"/>
       <c r="J147" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K148" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
       <c r="I149" s="7"/>
       <c r="J149" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K150" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D151" s="5"/>
       <c r="E151" s="5" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="7"/>
       <c r="J151" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J152" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K152" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="5" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D153" s="5"/>
       <c r="E153" s="5" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K153" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J154" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K154" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="5" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D155" s="5"/>
       <c r="E155" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K155" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G156" s="4"/>
       <c r="H156" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="5" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="4" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G158" s="4"/>
       <c r="H158" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K158" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="5" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D159" s="5"/>
       <c r="E159" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
       <c r="I159" s="7"/>
       <c r="J159" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="4" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F160" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>382</v>
+      </c>
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
       <c r="I160" s="6"/>
       <c r="J160" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="K160" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="5" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D161" s="5"/>
       <c r="E161" s="5" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K161" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="6"/>
       <c r="J162" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="5" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D163" s="5"/>
       <c r="E163" s="5" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K163" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="4" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G164" s="4"/>
       <c r="H164" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K164" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="5" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D165" s="5"/>
       <c r="E165" s="5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G165" s="5"/>
       <c r="H165" s="5" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K165" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="4" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G166" s="4"/>
       <c r="H166" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K166" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="5" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D167" s="5"/>
       <c r="E167" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="4" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G168" s="4"/>
       <c r="H168" s="4" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J168" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K168" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="5" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D169" s="5"/>
       <c r="E169" s="5" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
       <c r="H169" s="5"/>
       <c r="I169" s="7"/>
       <c r="J169" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
       <c r="I170" s="6"/>
       <c r="J170" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="5" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5" t="s">
-        <v>484</v>
+        <v>17</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K171" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="6"/>
       <c r="J172" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="5" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F173" s="5"/>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="7"/>
       <c r="J173" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G174" s="4"/>
       <c r="H174" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K174" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="5" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D175" s="5"/>
       <c r="E175" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K175" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G176" s="4"/>
       <c r="H176" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J176" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K176" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="5" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F177" s="5"/>
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="I177" s="7"/>
       <c r="J177" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="6"/>
       <c r="J178" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="5" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
@@ -7057,46 +7587,46 @@
       <c r="H179" s="5"/>
       <c r="I179" s="7"/>
       <c r="J179" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G180" s="4"/>
       <c r="H180" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K180" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="5" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
@@ -7106,910 +7636,910 @@
       <c r="H181" s="5"/>
       <c r="I181" s="7"/>
       <c r="J181" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G182" s="4"/>
       <c r="H182" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K182" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F183" s="5"/>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="7"/>
       <c r="J183" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
       <c r="I184" s="6"/>
       <c r="J184" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="5" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>27</v>
+        <v>664</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="G185" s="5"/>
       <c r="H185" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I185" s="7"/>
       <c r="J185" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K185" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="4" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J186" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K186" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D187" s="5"/>
       <c r="E187" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J187" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K187" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="G188" s="4"/>
       <c r="H188" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K188" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C189" s="5">
         <v>12355</v>
       </c>
       <c r="D189" s="5"/>
       <c r="E189" s="5" t="s">
-        <v>27</v>
+        <v>664</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="G189" s="5"/>
       <c r="H189" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J189" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K189" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="4" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="G190" s="4"/>
       <c r="H190" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I190" s="6"/>
       <c r="J190" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K190" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D191" s="5"/>
       <c r="E191" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="G191" s="5"/>
       <c r="H191" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I191" s="7"/>
       <c r="J191" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K191" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C192" s="4">
         <v>7676</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="G192" s="4"/>
       <c r="H192" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J192" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K192" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="5" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D193" s="5"/>
       <c r="E193" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>365</v>
+        <v>690</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>484</v>
+        <v>17</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K193" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="4" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J194" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K194" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D195" s="5"/>
       <c r="E195" s="5" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K195" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C196" s="4">
         <v>36363</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="G196" s="4"/>
       <c r="H196" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K196" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C197" s="5">
         <v>121212121</v>
       </c>
       <c r="D197" s="5"/>
       <c r="E197" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G197" s="5"/>
       <c r="H197" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K197" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="4" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J198" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K198" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C199" s="5">
         <v>111111111111</v>
       </c>
       <c r="D199" s="5"/>
       <c r="E199" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K199" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="4" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D200" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F200" s="4" t="s">
         <v>711</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F200" s="4" t="s">
-        <v>707</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J200" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K200" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K201" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="4" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J202" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K202" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>27</v>
+        <v>728</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K203" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="4" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J204" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K204" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="5" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G205" s="5"/>
       <c r="H205" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J205" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K205" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="4" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>27</v>
+        <v>728</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J206" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K206" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="5" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="H207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J207" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K207" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="208" spans="1:11">
       <c r="A208" s="4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J208" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K208" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="209" spans="1:11">
       <c r="A209" s="5" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C209" s="5">
         <v>7878787</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I209" s="7"/>
       <c r="J209" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K209" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="210" spans="1:11">
       <c r="A210" s="4" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="C210" s="4">
         <v>12121</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K210" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -8017,96 +8547,1307 @@
         <v>11111</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C211" s="5">
         <v>11111</v>
       </c>
       <c r="D211" s="5"/>
       <c r="E211" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="H211" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F211" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="G211" s="5"/>
-      <c r="H211" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="I211" s="7" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="J211" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K211" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="212" spans="1:11">
       <c r="A212" s="4" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C212" s="4">
         <v>1111</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J212" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K212" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="213" spans="1:11">
       <c r="A213" s="5" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="C213" s="5">
         <v>121233</v>
       </c>
       <c r="D213" s="5"/>
       <c r="E213" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K213" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="A214" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C214" s="4">
+        <v>123123</v>
+      </c>
+      <c r="D214" s="4"/>
+      <c r="E214" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I214" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J214" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K214" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="A215" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C215" s="5"/>
+      <c r="D215" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="G215" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="H215" s="5"/>
+      <c r="I215" s="7"/>
+      <c r="J215" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K215" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="A216" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="C216" s="4">
+        <v>412412</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="H216" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I216" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J216" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K216" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="A217" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D217" s="5"/>
+      <c r="E217" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G217" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="H217" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J217" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K217" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11">
+      <c r="A218" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="D218" s="4"/>
+      <c r="E218" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="G218" s="4"/>
+      <c r="H218" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I218" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J218" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K218" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="A219" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G219" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H219" s="5"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K219" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11">
+      <c r="A220" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="E220" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="H220" s="4"/>
+      <c r="I220" s="6"/>
+      <c r="J220" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K220" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="A221" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C221" s="5"/>
+      <c r="D221" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="G221" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="H221" s="5"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K221" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="A222" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C222" s="4"/>
+      <c r="D222" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="H222" s="4"/>
+      <c r="I222" s="6"/>
+      <c r="J222" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K222" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="A223" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="C223" s="5"/>
+      <c r="D223" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="H223" s="5"/>
+      <c r="I223" s="7"/>
+      <c r="J223" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K223" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C224" s="4"/>
+      <c r="D224" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="H224" s="4"/>
+      <c r="I224" s="6"/>
+      <c r="J224" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K224" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11">
+      <c r="A225" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="C225" s="5"/>
+      <c r="D225" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="E225" s="5"/>
+      <c r="F225" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="H225" s="5"/>
+      <c r="I225" s="7"/>
+      <c r="J225" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K225" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11">
+      <c r="A226" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C226" s="4"/>
+      <c r="D226" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="E226" s="4"/>
+      <c r="F226" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="H226" s="4"/>
+      <c r="I226" s="6"/>
+      <c r="J226" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K226" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11">
+      <c r="A227" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="D227" s="5"/>
+      <c r="E227" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="G227" s="5"/>
+      <c r="H227" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I227" s="7"/>
+      <c r="J227" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K227" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="A228" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="C228" s="4">
+        <v>78784545</v>
+      </c>
+      <c r="D228" s="4"/>
+      <c r="E228" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="I228" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J228" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K228" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="A229" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="C229" s="5">
+        <v>455678</v>
+      </c>
+      <c r="D229" s="5"/>
+      <c r="E229" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="H229" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J229" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K229" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="A230" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="E230" s="4"/>
+      <c r="F230" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="H230" s="4"/>
+      <c r="I230" s="6"/>
+      <c r="J230" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K230" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="A231" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="C231" s="5">
+        <v>2121211221122121</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="H231" s="5"/>
+      <c r="I231" s="7"/>
+      <c r="J231" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K231" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="A232" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="C232" s="4"/>
+      <c r="D232" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="E232" s="4"/>
+      <c r="F232" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="H232" s="4"/>
+      <c r="I232" s="6"/>
+      <c r="J232" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K232" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="H233" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I233" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J233" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K233" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="A234" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="D234" s="4"/>
+      <c r="E234" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G234" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="H234" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I234" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J234" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K234" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C235" s="5"/>
+      <c r="D235" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="E235" s="5"/>
+      <c r="F235" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="H235" s="5"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K235" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="A236" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G236" s="4"/>
+      <c r="H236" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I236" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J236" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K236" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C237" s="5"/>
+      <c r="D237" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="H237" s="5"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K237" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="A238" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C238" s="4"/>
+      <c r="D238" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="E238" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="H238" s="4"/>
+      <c r="I238" s="6"/>
+      <c r="J238" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K238" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11">
+      <c r="A239" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="C239" s="5"/>
+      <c r="D239" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="H239" s="5"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K239" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11">
+      <c r="A240" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="G240" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="H240" s="4"/>
+      <c r="I240" s="6"/>
+      <c r="J240" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K240" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11">
+      <c r="A241" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C241" s="5"/>
+      <c r="D241" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="H241" s="5"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K241" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11">
+      <c r="A242" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="C242" s="4"/>
+      <c r="D242" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="E242" s="4"/>
+      <c r="F242" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="H242" s="4"/>
+      <c r="I242" s="6"/>
+      <c r="J242" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K242" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11">
+      <c r="A243" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="E243" s="5"/>
+      <c r="F243" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="H243" s="5"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K243" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11">
+      <c r="A244" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="E244" s="4"/>
+      <c r="F244" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="H244" s="4"/>
+      <c r="I244" s="6"/>
+      <c r="J244" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K244" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11">
+      <c r="A245" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="C245" s="5"/>
+      <c r="D245" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="H245" s="5"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K245" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11">
+      <c r="A246" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="C246" s="4"/>
+      <c r="D246" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="E246" s="4"/>
+      <c r="F246" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="H246" s="4"/>
+      <c r="I246" s="6"/>
+      <c r="J246" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K246" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11">
+      <c r="A247" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="C247" s="5"/>
+      <c r="D247" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="E247" s="5"/>
+      <c r="F247" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="H247" s="5"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K247" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11">
+      <c r="A248" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="C248" s="4"/>
+      <c r="D248" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="G248" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="H248" s="4"/>
+      <c r="I248" s="6"/>
+      <c r="J248" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K248" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11">
+      <c r="A249" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I249" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J249" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K249" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11">
+      <c r="A250" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="C250" s="4"/>
+      <c r="D250" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="H250" s="4"/>
+      <c r="I250" s="6"/>
+      <c r="J250" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K250" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11">
+      <c r="A251" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="C251" s="5"/>
+      <c r="D251" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="E251" s="5"/>
+      <c r="F251" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="H251" s="5"/>
+      <c r="I251" s="7"/>
+      <c r="J251" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K251" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11">
+      <c r="A252" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="E252" s="4"/>
+      <c r="F252" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H252" s="4"/>
+      <c r="I252" s="6"/>
+      <c r="J252" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K252" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11">
+      <c r="A253" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="G253" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H253" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I253" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J253" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K253" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11">
+      <c r="A254" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I254" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J254" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K254" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
